--- a/public/templates/initiative/initiativesheet.xlsx
+++ b/public/templates/initiative/initiativesheet.xlsx
@@ -1,110 +1,572 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\web\ugoki\kensyu\document\sakura_set\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F477055-C6E2-43C3-BD85-1BEB9EC5D72C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{A7C6E258-9859-436F-AC8F-9FD773BF0FFB}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="取り組み記録" sheetId="2" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="20">
+  <si>
+    <t>フェースシート</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>④面談</t>
+  </si>
+  <si>
+    <t>予定日</t>
+  </si>
+  <si>
+    <t>実施日</t>
+  </si>
+  <si>
+    <t>⑤</t>
+  </si>
+  <si>
+    <t>記入日</t>
+  </si>
+  <si>
+    <t>⑥面談</t>
+  </si>
+  <si>
+    <t>氏名</t>
+  </si>
+  <si>
+    <t>振り返りシート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>か月目</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>年</t>
+    <rPh sb="0" eb="1">
+      <t>ネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>月</t>
+    <rPh sb="0" eb="1">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日</t>
+    <rPh sb="0" eb="1">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力箇所</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>さくらセット取り組み記録</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実施日</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>① ② ③</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>さくらセットの手引き　2「さくらセット」活用の流れ　①～⑥　準拠</t>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="13">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="31">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -245,16 +707,448 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57773EF4-CADA-4B44-A12A-33A2F499CC42}">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData/>
-  <drawing r:id="rId1"/>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="4.625" customWidth="1"/>
+    <col min="2" max="2" width="16.625" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="6.875" customWidth="1"/>
+    <col min="5" max="5" width="3.125" customWidth="1"/>
+    <col min="6" max="6" width="4.5" customWidth="1"/>
+    <col min="7" max="7" width="3.125" customWidth="1"/>
+    <col min="8" max="8" width="4.5" customWidth="1"/>
+    <col min="9" max="9" width="3.125" customWidth="1"/>
+    <col min="10" max="10" width="13.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="26"/>
+      <c r="J1" s="27"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="19"/>
+      <c r="B2" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="16"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" s="21"/>
+      <c r="B3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="17"/>
+      <c r="E3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="17"/>
+      <c r="G3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="6"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A4" s="21"/>
+      <c r="B4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="17"/>
+      <c r="E4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A5" s="21"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="17"/>
+      <c r="E5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10" ht="70.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="23"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="28"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="30"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A7" s="20"/>
+      <c r="B7" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="14"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A8" s="21"/>
+      <c r="B8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="17"/>
+      <c r="G8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="17"/>
+      <c r="I8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A9" s="21"/>
+      <c r="B9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="17"/>
+      <c r="E9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="17"/>
+      <c r="G9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="17"/>
+      <c r="I9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A10" s="21"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="17"/>
+      <c r="E10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="17"/>
+      <c r="G10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="17"/>
+      <c r="I10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:10" ht="70.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="23"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="28"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="30"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A12" s="20"/>
+      <c r="B12" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A13" s="21"/>
+      <c r="B13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="17"/>
+      <c r="G13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A14" s="21"/>
+      <c r="B14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="17"/>
+      <c r="E14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="17"/>
+      <c r="G14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="17"/>
+      <c r="I14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A15" s="21"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="17"/>
+      <c r="E15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="17"/>
+      <c r="G15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="17"/>
+      <c r="I15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="6"/>
+    </row>
+    <row r="16" spans="1:10" ht="56.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="23"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="28"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="30"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A18" s="21"/>
+      <c r="B18" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="17"/>
+      <c r="E18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="17"/>
+      <c r="G18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="17"/>
+      <c r="I18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="6"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A19" s="21"/>
+      <c r="B19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="17"/>
+      <c r="E19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="17"/>
+      <c r="G19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="17"/>
+      <c r="I19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A20" s="21"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="17"/>
+      <c r="G20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="6"/>
+    </row>
+    <row r="21" spans="1:10" ht="70.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="23"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="28"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="30"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A24" s="25"/>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D16:J16"/>
+    <mergeCell ref="D21:J21"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.98425196850393704" right="0.98425196850393704" top="0.98425196850393704" bottom="0.98425196850393704" header="0.39370078740157483" footer="0.39370078740157483"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>